--- a/01_Input/00_CO Validation/Yemen - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Yemen - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27018"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ERRY 3\benficaries numbers from HQ 3 June\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="13_ncr:1_{3DE8FC2F-91BA-4E5A-A2A1-F58E56257A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9251040-0477-46C0-AE56-B527062703C9}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{3DE8FC2F-91BA-4E5A-A2A1-F58E56257A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F072974-52DE-4E34-BE2B-4606B36772AE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="142">
   <si>
     <t>Project ID</t>
   </si>
@@ -208,9 +208,6 @@
   </si>
   <si>
     <t>Health Services</t>
-  </si>
-  <si>
-    <t>72 by 2018 through ERRY I</t>
   </si>
   <si>
     <t>72 solar-powered vaccine refrigerators installed in health centers, benefiting 60,000 individuals by 2022</t>
@@ -496,6 +493,9 @@
   </si>
   <si>
     <t>3 solar pumping systems + 1 solar powered desalination systems</t>
+  </si>
+  <si>
+    <t>72 by 2018 through ERRY I</t>
   </si>
   <si>
     <r>
@@ -1749,14 +1749,12 @@
       <c r="F8" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="21" t="s">
-        <v>46</v>
-      </c>
+      <c r="G8" s="21"/>
       <c r="H8" s="26">
         <v>60000</v>
       </c>
       <c r="I8" s="51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J8" s="23" t="s">
         <v>25</v>
@@ -1765,7 +1763,7 @@
       <c r="L8" s="54"/>
       <c r="M8" s="46"/>
       <c r="N8" s="47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O8" s="47" t="s">
         <v>27</v>
@@ -1783,10 +1781,10 @@
       <c r="C9" s="52"/>
       <c r="D9" s="23"/>
       <c r="E9" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="29" t="s">
         <v>49</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>50</v>
       </c>
       <c r="G9" s="29">
         <v>0</v>
@@ -1795,7 +1793,7 @@
         <v>713</v>
       </c>
       <c r="I9" s="51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J9" s="23" t="s">
         <v>25</v>
@@ -1819,10 +1817,10 @@
         <v>135714</v>
       </c>
       <c r="B10" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="52" t="s">
         <v>52</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>53</v>
       </c>
       <c r="D10" s="23">
         <v>2727783</v>
@@ -1831,16 +1829,16 @@
         <v>45</v>
       </c>
       <c r="F10" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="32" t="s">
         <v>54</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>55</v>
       </c>
       <c r="H10" s="26">
         <v>100000</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J10" s="23" t="s">
         <v>25</v>
@@ -1851,7 +1849,7 @@
       </c>
       <c r="M10" s="46"/>
       <c r="N10" s="47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O10" s="47" t="s">
         <v>27</v>
@@ -1872,13 +1870,13 @@
         <v>21</v>
       </c>
       <c r="F11" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="H11" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="I11" s="20"/>
       <c r="J11" s="23" t="s">
@@ -1904,10 +1902,10 @@
       <c r="C12" s="52"/>
       <c r="D12" s="23"/>
       <c r="E12" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>60</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="29">
         <v>0</v>
@@ -1916,7 +1914,7 @@
         <v>0.3</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J12" s="23" t="s">
         <v>25</v>
@@ -1924,14 +1922,14 @@
       <c r="K12" s="47"/>
       <c r="L12" s="54"/>
       <c r="M12" s="43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N12" s="47"/>
       <c r="O12" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="P12" s="47" t="s">
         <v>64</v>
-      </c>
-      <c r="P12" s="47" t="s">
-        <v>65</v>
       </c>
       <c r="Q12" s="47"/>
       <c r="R12" s="47"/>
@@ -1943,10 +1941,10 @@
       <c r="C13" s="52"/>
       <c r="D13" s="23"/>
       <c r="E13" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13" s="29">
         <v>2</v>
@@ -1955,7 +1953,7 @@
         <v>0.2</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J13" s="23" t="s">
         <v>25</v>
@@ -1963,14 +1961,14 @@
       <c r="K13" s="47"/>
       <c r="L13" s="54"/>
       <c r="M13" s="43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N13" s="47"/>
       <c r="O13" s="47" t="s">
         <v>27</v>
       </c>
       <c r="P13" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q13" s="47"/>
       <c r="R13" s="47"/>
@@ -1982,10 +1980,10 @@
       <c r="C14" s="52"/>
       <c r="D14" s="23"/>
       <c r="E14" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="21" t="s">
         <v>69</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>70</v>
       </c>
       <c r="G14" s="29">
         <v>0</v>
@@ -1994,7 +1992,7 @@
         <v>500</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J14" s="23" t="s">
         <v>25</v>
@@ -2018,7 +2016,7 @@
         <v>43</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G15" s="29">
         <v>1</v>
@@ -2027,7 +2025,7 @@
         <v>6000</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J15" s="23" t="s">
         <v>25</v>
@@ -2042,7 +2040,7 @@
         <v>27</v>
       </c>
       <c r="P15" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="47"/>
       <c r="R15" s="47"/>
@@ -2053,10 +2051,10 @@
         <v>137393</v>
       </c>
       <c r="B16" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="52" t="s">
         <v>74</v>
-      </c>
-      <c r="C16" s="52" t="s">
-        <v>75</v>
       </c>
       <c r="D16" s="23">
         <v>463769</v>
@@ -2065,7 +2063,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" s="29">
         <v>1</v>
@@ -2075,7 +2073,7 @@
       </c>
       <c r="I16" s="21"/>
       <c r="J16" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K16" s="47"/>
       <c r="L16" s="54" t="s">
@@ -2083,13 +2081,13 @@
       </c>
       <c r="M16" s="46"/>
       <c r="N16" s="47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O16" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="P16" s="47" t="s">
         <v>64</v>
-      </c>
-      <c r="P16" s="47" t="s">
-        <v>65</v>
       </c>
       <c r="Q16" s="47"/>
       <c r="R16" s="47"/>
@@ -2101,17 +2099,17 @@
       <c r="C17" s="56"/>
       <c r="D17" s="55"/>
       <c r="E17" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G17" s="29"/>
       <c r="H17" s="29">
         <v>11200</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J17" s="23"/>
       <c r="K17" s="47"/>
@@ -2119,10 +2117,10 @@
       <c r="M17" s="46"/>
       <c r="N17" s="47"/>
       <c r="O17" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="P17" s="47" t="s">
         <v>64</v>
-      </c>
-      <c r="P17" s="47" t="s">
-        <v>65</v>
       </c>
       <c r="Q17" s="47"/>
       <c r="R17" s="47"/>
@@ -2134,30 +2132,28 @@
       <c r="C18" s="56"/>
       <c r="D18" s="55"/>
       <c r="E18" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="29"/>
+      <c r="H18" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="G18" s="29">
-        <v>3</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="I18" s="21"/>
       <c r="J18" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K18" s="47"/>
       <c r="L18" s="54"/>
       <c r="M18" s="46"/>
       <c r="N18" s="47"/>
       <c r="O18" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="P18" s="47" t="s">
         <v>64</v>
-      </c>
-      <c r="P18" s="47" t="s">
-        <v>65</v>
       </c>
       <c r="Q18" s="47"/>
       <c r="R18" s="47"/>
@@ -2169,10 +2165,10 @@
       <c r="C19" s="52"/>
       <c r="D19" s="23"/>
       <c r="E19" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G19" s="29">
         <v>30</v>
@@ -2182,7 +2178,7 @@
       </c>
       <c r="I19" s="21"/>
       <c r="J19" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K19" s="47"/>
       <c r="L19" s="54"/>
@@ -2342,7 +2338,7 @@
         <v>24</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I2" s="22"/>
       <c r="J2" s="23" t="s">
@@ -2403,10 +2399,10 @@
         <v>33</v>
       </c>
       <c r="G4" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="66" t="s">
         <v>84</v>
-      </c>
-      <c r="H4" s="66" t="s">
-        <v>85</v>
       </c>
       <c r="I4" s="22"/>
       <c r="J4" s="23" t="s">
@@ -2464,13 +2460,13 @@
         <v>28</v>
       </c>
       <c r="F6" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="66" t="s">
+      <c r="H6" s="66" t="s">
         <v>87</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>88</v>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="33" t="s">
@@ -2500,13 +2496,13 @@
         <v>33</v>
       </c>
       <c r="G7" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="66" t="s">
+      <c r="I7" s="21" t="s">
         <v>90</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>91</v>
       </c>
       <c r="J7" s="33" t="s">
         <v>25</v>
@@ -2535,13 +2531,13 @@
         <v>29</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="H8" s="26">
         <v>60000</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J8" s="23" t="s">
         <v>25</v>
@@ -2562,10 +2558,10 @@
       <c r="C9" s="61"/>
       <c r="D9" s="60"/>
       <c r="E9" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="29" t="s">
         <v>49</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>50</v>
       </c>
       <c r="G9" s="29">
         <v>0</v>
@@ -2574,7 +2570,7 @@
         <v>713</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J9" s="23" t="s">
         <v>25</v>
@@ -2594,10 +2590,10 @@
         <v>135714</v>
       </c>
       <c r="B10" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>52</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>53</v>
       </c>
       <c r="D10" s="30">
         <v>2727783</v>
@@ -2606,16 +2602,16 @@
         <v>45</v>
       </c>
       <c r="F10" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="32" t="s">
         <v>54</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>55</v>
       </c>
       <c r="H10" s="26">
         <v>100000</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J10" s="23" t="s">
         <v>25</v>
@@ -2641,13 +2637,13 @@
         <v>21</v>
       </c>
       <c r="F11" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="H11" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="23" t="s">
@@ -2669,10 +2665,10 @@
       <c r="C12" s="31"/>
       <c r="D12" s="30"/>
       <c r="E12" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>60</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="29">
         <v>0</v>
@@ -2687,13 +2683,13 @@
       <c r="K12" s="24"/>
       <c r="L12" s="58"/>
       <c r="M12" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="O12" t="s">
         <v>63</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>64</v>
-      </c>
-      <c r="P12" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="118.5" customHeight="1">
@@ -2702,16 +2698,16 @@
       <c r="C13" s="31"/>
       <c r="D13" s="30"/>
       <c r="E13" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13" s="29">
         <v>2</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I13" s="21"/>
       <c r="J13" s="23" t="s">
@@ -2720,13 +2716,13 @@
       <c r="K13" s="24"/>
       <c r="L13" s="58"/>
       <c r="M13" s="43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O13" t="s">
         <v>27</v>
       </c>
       <c r="P13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="91.5">
@@ -2735,10 +2731,10 @@
       <c r="C14" s="31"/>
       <c r="D14" s="30"/>
       <c r="E14" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="21" t="s">
         <v>69</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>70</v>
       </c>
       <c r="G14" s="29">
         <v>0</v>
@@ -2747,7 +2743,7 @@
         <v>500</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J14" s="23" t="s">
         <v>25</v>
@@ -2765,13 +2761,13 @@
         <v>43</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G15" s="29">
         <v>1</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I15" s="21"/>
       <c r="J15" s="23" t="s">
@@ -2786,7 +2782,7 @@
         <v>27</v>
       </c>
       <c r="P15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="91.5">
@@ -2794,10 +2790,10 @@
         <v>137393</v>
       </c>
       <c r="B16" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="31" t="s">
         <v>74</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>75</v>
       </c>
       <c r="D16" s="30">
         <v>463769</v>
@@ -2806,7 +2802,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" s="29">
         <v>1</v>
@@ -2816,7 +2812,7 @@
       </c>
       <c r="I16" s="21"/>
       <c r="J16" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K16" s="24"/>
       <c r="L16" s="57" t="s">
@@ -2824,10 +2820,10 @@
       </c>
       <c r="M16" s="17"/>
       <c r="O16" t="s">
+        <v>63</v>
+      </c>
+      <c r="P16" t="s">
         <v>64</v>
-      </c>
-      <c r="P16" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2836,7 +2832,7 @@
       <c r="C17" s="61"/>
       <c r="D17" s="60"/>
       <c r="E17" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>94</v>
@@ -2846,17 +2842,17 @@
         <v>11200</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J17" s="23"/>
       <c r="K17" s="24"/>
       <c r="L17" s="58"/>
       <c r="M17" s="17"/>
       <c r="O17" t="s">
+        <v>63</v>
+      </c>
+      <c r="P17" t="s">
         <v>64</v>
-      </c>
-      <c r="P17" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="91.5">
@@ -2865,29 +2861,29 @@
       <c r="C18" s="61"/>
       <c r="D18" s="60"/>
       <c r="E18" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G18" s="29">
         <v>3</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I18" s="21"/>
       <c r="J18" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K18" s="24"/>
       <c r="L18" s="58"/>
       <c r="M18" s="17"/>
       <c r="O18" t="s">
+        <v>63</v>
+      </c>
+      <c r="P18" t="s">
         <v>64</v>
-      </c>
-      <c r="P18" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="91.5">
@@ -2896,10 +2892,10 @@
       <c r="C19" s="31"/>
       <c r="D19" s="30"/>
       <c r="E19" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G19" s="29">
         <v>30</v>
@@ -2909,7 +2905,7 @@
       </c>
       <c r="I19" s="21"/>
       <c r="J19" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K19" s="24"/>
       <c r="L19" s="59"/>
@@ -3110,7 +3106,7 @@
       <c r="C5" s="7"/>
       <c r="D5" s="6"/>
       <c r="E5" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>37</v>
@@ -3135,7 +3131,7 @@
         <v>28</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>101</v>
@@ -3166,7 +3162,7 @@
         <v>103</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>25</v>
@@ -3184,10 +3180,10 @@
         <v>33</v>
       </c>
       <c r="G8" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>46</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>47</v>
       </c>
       <c r="I8" s="11"/>
       <c r="J8" s="12" t="s">
@@ -3200,16 +3196,16 @@
       <c r="C9" s="7"/>
       <c r="D9" s="6"/>
       <c r="E9" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="14" t="s">
         <v>49</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>50</v>
       </c>
       <c r="G9" s="14">
         <v>0</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="12" t="s">
@@ -3221,10 +3217,10 @@
         <v>135714</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="D10" s="6">
         <v>2727783</v>
@@ -3233,10 +3229,10 @@
         <v>45</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>104</v>
@@ -3257,10 +3253,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="15" t="s">
         <v>57</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>106</v>
@@ -3276,10 +3272,10 @@
       <c r="C12" s="7"/>
       <c r="D12" s="6"/>
       <c r="E12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>60</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="14">
         <v>0</v>
@@ -3298,16 +3294,16 @@
       <c r="C13" s="7"/>
       <c r="D13" s="6"/>
       <c r="E13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13" s="14">
         <v>2</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="12" t="s">
@@ -3320,10 +3316,10 @@
       <c r="C14" s="7"/>
       <c r="D14" s="6"/>
       <c r="E14" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="G14" s="14">
         <v>0</v>
@@ -3332,7 +3328,7 @@
         <v>108</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>25</v>
@@ -3347,7 +3343,7 @@
         <v>43</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
@@ -3365,10 +3361,10 @@
         <v>137393</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>75</v>
       </c>
       <c r="D16" s="6">
         <v>463769</v>
@@ -3387,7 +3383,7 @@
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="87">
@@ -3396,7 +3392,7 @@
       <c r="C17" s="7"/>
       <c r="D17" s="6"/>
       <c r="E17" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>112</v>
@@ -3409,7 +3405,7 @@
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="87">
@@ -3418,10 +3414,10 @@
       <c r="C18" s="7"/>
       <c r="D18" s="6"/>
       <c r="E18" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G18" s="14">
         <v>30</v>
@@ -3431,7 +3427,7 @@
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -3490,7 +3486,7 @@
     <row r="3" spans="1:3">
       <c r="A3" s="62"/>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
         <v>119</v>
@@ -3546,7 +3542,7 @@
     <row r="9" spans="1:3">
       <c r="A9" s="63"/>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
         <v>127</v>
@@ -3577,7 +3573,7 @@
         <v>132</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
         <v>133</v>
@@ -3586,7 +3582,7 @@
     <row r="13" spans="1:3">
       <c r="A13" s="65"/>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
         <v>134</v>
@@ -3635,12 +3631,51 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Abdo Seif</DisplayName>
+        <AccountId>1919</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fuad Ali</DisplayName>
+        <AccountId>1396</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Mohammed Sallam</DisplayName>
+        <AccountId>2139</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Amal Aldababseh</DisplayName>
+        <AccountId>1045</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Riad Meddeb</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Benjamin Keller</DisplayName>
+        <AccountId>1227</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3893,55 +3928,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Abdo Seif</DisplayName>
-        <AccountId>1919</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fuad Ali</DisplayName>
-        <AccountId>1396</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Mohammed Sallam</DisplayName>
-        <AccountId>2139</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Amal Aldababseh</DisplayName>
-        <AccountId>1045</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Riad Meddeb</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Benjamin Keller</DisplayName>
-        <AccountId>1227</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED76DDC8-0C2A-42A8-8991-BD9F8D7F2EB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98E0B7DD-E5CA-4A63-8AD0-7BC5AD48CEFE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3949,5 +3945,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98E0B7DD-E5CA-4A63-8AD0-7BC5AD48CEFE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED76DDC8-0C2A-42A8-8991-BD9F8D7F2EB1}"/>
 </file>
--- a/01_Input/00_CO Validation/Yemen - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Yemen - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ERRY 3\benficaries numbers from HQ 3 June\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="262" documentId="13_ncr:1_{3DE8FC2F-91BA-4E5A-A2A1-F58E56257A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2975FEBC-6BB2-435F-9B35-B499A4867F35}"/>
+  <xr:revisionPtr revIDLastSave="397" documentId="13_ncr:1_{3DE8FC2F-91BA-4E5A-A2A1-F58E56257A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC9FC8F6-7332-437C-86B4-AAFDB5CD40C8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="172">
   <si>
     <t>Project ID</t>
   </si>
@@ -122,7 +122,7 @@
     <t>5600 by 2018 through ERRY I</t>
   </si>
   <si>
-    <t>EU and SIDA</t>
+    <t>EU, SIDA</t>
   </si>
   <si>
     <t>Non-VF</t>
@@ -164,7 +164,25 @@
 </t>
   </si>
   <si>
-    <t>to the CO: Please estimate number of beneficiaries.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>182,000</t>
+    </r>
   </si>
   <si>
     <t>Small Enterprises</t>
@@ -208,75 +226,6 @@
     </r>
   </si>
   <si>
-    <t>Water Services</t>
-  </si>
-  <si>
-    <t>3 solar pumping systems + 1 solar powered desalination systems
-4 by 2018
-818 Households, 1871 women, 2003 men, 243 girls and 345 boys. Total individual 4462
-4 solar water pumping systems installed supporting 4 community drinking water projects by 2022
-805 HHs
-2460 male, 3735 female. Total individual 6195</t>
-  </si>
-  <si>
-    <t>Health Services</t>
-  </si>
-  <si>
-    <t>72 solar-powered vaccine refrigerators installed in health centers, benefiting 60,000 individuals by 2022</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>Capacity Building Training</t>
-  </si>
-  <si>
-    <t># of trained and certified women and youth in solar system installation who have adopted solar innovation</t>
-  </si>
-  <si>
-    <t>713 women and youth received vocational training in solar system installation by 2022</t>
-  </si>
-  <si>
-    <t>Supporting Resilient Livelihoods, Food Security and Clim</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00135714</t>
-  </si>
-  <si>
-    <t>Number of beneficiaries
-public facilities and households provided with access to renewable energy solutions (disaggregated by facility/household, men/women-headed, sector, and location, women institutions/services ), with support of the intervention</t>
-  </si>
-  <si>
-    <t>182000 Individuals through ERRY I &amp; II</t>
-  </si>
-  <si>
-    <t>The category of this intervention includes education, health, and water.
-100 facilities supported with solar systems benfiting 100,000 Individuals  by 2024</t>
-  </si>
-  <si>
-    <t>Number of public facilities and households provided with access to renewable energy solutions (disaggregated by facility/household, men/women-headed, sector, and location, women institutions/services ), with support of the intervention</t>
-  </si>
-  <si>
-    <t>13160 through ERRY I &amp; II</t>
-  </si>
-  <si>
-    <t>500 HH</t>
-  </si>
-  <si>
-    <t>Some Sources</t>
-  </si>
-  <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
-    <t>Number of solar/wind energy mini-grids established in small and medium markets and commercial centers and shops, with support of the intervention</t>
-  </si>
-  <si>
-    <t>2 Solar and Wind minigrids
-Total Capacity is 0.3 Mw
-by 2024</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -284,7 +233,124 @@
         <color rgb="FFFF0000"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t xml:space="preserve">to the CO: Please estimate the number of MW (is this value per minigrid, or total?)
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>752</t>
+    </r>
+  </si>
+  <si>
+    <t>Water Services</t>
+  </si>
+  <si>
+    <t>3 solar pumping systems + 1 solar powered desalination systems
+4 by 2018
+818 Households, 1871 women, 2003 men, 243 girls and 345 boys. Total individual 4462
+4 solar water pumping systems installed supporting 4 community drinking water projects by 2022
+805 HHs
+2460 male, 3735 female. Total individual 6195</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>10,657</t>
+    </r>
+  </si>
+  <si>
+    <t>Health Services</t>
+  </si>
+  <si>
+    <t>72 solar-powered vaccine refrigerators installed in health centers, benefiting 60,000 individuals by 2022</t>
+  </si>
+  <si>
+    <t>60,000</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t># of trained and certified women and youth in solar system installation who have adopted solar innovation</t>
+  </si>
+  <si>
+    <t>713 women and youth received vocational training in solar system installation by 2022</t>
+  </si>
+  <si>
+    <t>Supporting Resilient Livelihoods, Food Security and Clim</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00135714</t>
+  </si>
+  <si>
+    <t>Number of beneficiaries
+public facilities and households provided with access to renewable energy solutions (disaggregated by facility/household, men/women-headed, sector, and location, women institutions/services ), with support of the intervention</t>
+  </si>
+  <si>
+    <t>182000 Individuals through ERRY I &amp; II</t>
+  </si>
+  <si>
+    <t>The category of this intervention includes education, health, and water.
+140 facilities supported with solar systems benfiting 250,000 Individuals  by 2024</t>
+  </si>
+  <si>
+    <t>Number of public facilities and households provided with access to renewable energy solutions (disaggregated by facility/household, men/women-headed, sector, and location, women institutions/services ), with support of the intervention</t>
+  </si>
+  <si>
+    <t>13160 through ERRY I &amp; II</t>
+  </si>
+  <si>
+    <t>500 HH</t>
+  </si>
+  <si>
+    <t>Some Sources</t>
+  </si>
+  <si>
+    <t>3500</t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>Number of solar/wind energy mini-grids established in small and medium markets and commercial centers and shops, with support of the intervention</t>
+  </si>
+  <si>
+    <t>1 Solar and Wind minigrids
+Total Capacity is 0.2 Mw
+by 2024</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -294,28 +360,33 @@
         <color rgb="FF0070C0"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>it is Total</t>
+      <t xml:space="preserve">it is Total
+</t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>the target amend to be one minigrid, and total capacity is 0.2MW</t>
+    </r>
   </si>
   <si>
     <t>Renewable Energy</t>
   </si>
   <si>
-    <t>Support waste to energy and water desalination business initiatives with the engagement women, youths and private sector for enviroment protection and improvement in collaboration with SDGs Climate initiative.
-Number of waste to energy (WtE) plants established</t>
-  </si>
-  <si>
-    <t>2 waste to energy plants
-0.2 Mw
-by 2024</t>
-  </si>
-  <si>
-    <t>Waste</t>
-  </si>
-  <si>
-    <t>Energy Efficiency</t>
-  </si>
-  <si>
     <t>Entrepreneurship Training</t>
   </si>
   <si>
@@ -325,7 +396,10 @@
     <t>Training and seed grants</t>
   </si>
   <si>
-    <t>Support waste to energy and water desalination business initiatives with the engagement women, youths and private sector for enviroment protection and improvement in collaboration with SDGs Climate initiative.
+    <t>500</t>
+  </si>
+  <si>
+    <t>Support water desalination business initiatives with the engagement women, youths and private sector for enviroment protection and improvement in collaboration with SDGs Climate initiative.
 Number of Water Desalination established</t>
   </si>
   <si>
@@ -333,31 +407,65 @@
 initial estimation is 6,000 individual</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>5000</t>
+    </r>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
     <t>Renewable Energy Improved Access to Health Services</t>
   </si>
   <si>
     <t>http://open.undp.org/projects/00137393</t>
+  </si>
+  <si>
+    <t>4 Hospitals
+208,000 indviduals</t>
+  </si>
+  <si>
+    <t>4 Hospitals
+205,000 indvidual</t>
+  </si>
+  <si>
+    <t>208K is the number of patients benefit from the solar intervention in the 4 Hospitals.</t>
+  </si>
+  <si>
+    <t>KUWAIT FUND FOR ARAB ECONOMIC DEVELOPMENT</t>
   </si>
   <si>
     <t xml:space="preserve">Number of beneficiaries
 </t>
   </si>
   <si>
-    <t>KUWAIT FUND FOR ARAB ECONOMIC DEVELOPMENT</t>
-  </si>
-  <si>
-    <t>32 microgrid stations by 2023</t>
-  </si>
-  <si>
-    <t>Unknown</t>
+    <t>41 microgrid stations by 2024</t>
+  </si>
+  <si>
+    <t>11200</t>
   </si>
   <si>
     <t>MW
 Indicator 3: # solar microgrids stations have supported households/commercial places to access clean energy</t>
   </si>
   <si>
-    <t xml:space="preserve">
-0.481</t>
+    <t>4800</t>
   </si>
   <si>
     <t>Indicator 4: # number of women and men have improved access to sustained income through solar microgrids
@@ -365,6 +473,9 @@
 Target: 500</t>
   </si>
   <si>
+    <t>360</t>
+  </si>
+  <si>
     <t>Category</t>
   </si>
   <si>
@@ -372,6 +483,9 @@
   </si>
   <si>
     <t>7,560 HH</t>
+  </si>
+  <si>
+    <t>EU and SIDA</t>
   </si>
   <si>
     <t>Agricultural Services</t>
@@ -428,6 +542,9 @@
     </r>
   </si>
   <si>
+    <t>to the CO: Please estimate number of beneficiaries.</t>
+  </si>
+  <si>
     <t># of WUAs supported to promote efficient water and land management</t>
   </si>
   <si>
@@ -523,6 +640,10 @@
   </si>
   <si>
     <t>Capacity Training</t>
+  </si>
+  <si>
+    <t>The category of this intervention includes education, health, and water.
+100 facilities supported with solar systems benfiting 100,000 Individuals  by 2024</t>
   </si>
   <si>
     <r>
@@ -556,6 +677,40 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t xml:space="preserve">to the CO: Please estimate the number of MW (is this value per minigrid, or total?)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>it is Total</t>
+    </r>
+  </si>
+  <si>
+    <t>Support waste to energy and water desalination business initiatives with the engagement women, youths and private sector for enviroment protection and improvement in collaboration with SDGs Climate initiative.
+Number of waste to energy (WtE) plants established</t>
+  </si>
+  <si>
+    <t>2 waste to energy plants
+0.2 Mw
+by 2024</t>
+  </si>
+  <si>
+    <t>Support waste to energy and water desalination business initiatives with the engagement women, youths and private sector for enviroment protection and improvement in collaboration with SDGs Climate initiative.
+Number of Water Desalination established</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 80,000</t>
   </si>
@@ -564,6 +719,13 @@
   </si>
   <si>
     <t>benfiting individuals</t>
+  </si>
+  <si>
+    <t>32 microgrid stations by 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+0.481</t>
   </si>
   <si>
     <t>7,560 HHs supported with solar household solutions by 2022</t>
@@ -732,7 +894,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -817,8 +982,20 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -834,6 +1011,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -982,7 +1165,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1090,23 +1273,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1139,6 +1313,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1159,6 +1354,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1477,7 +1684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71540FF0-4F8F-4A4D-B57B-3E6D893C973C}">
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.28515625" bestFit="1" customWidth="1"/>
@@ -1488,6 +1695,7 @@
     <col min="8" max="8" width="28.140625" customWidth="1"/>
     <col min="9" max="9" width="32.7109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="63"/>
     <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.28515625" style="36" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -1495,6 +1703,9 @@
     <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.28515625" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" customWidth="1"/>
+    <col min="28" max="28" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="45.75">
@@ -1528,37 +1739,37 @@
       <c r="J1" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="42" t="s">
+      <c r="K1" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="56" t="s">
+      <c r="L1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="57" t="s">
+      <c r="M1" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="56" t="s">
+      <c r="N1" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="56" t="s">
+      <c r="O1" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="57" t="s">
+      <c r="P1" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="57" t="s">
+      <c r="Q1" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="58" t="s">
+      <c r="R1" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="59" t="s">
+      <c r="S1" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="58" t="s">
+      <c r="T1" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="59" t="s">
+      <c r="U1" s="56" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1569,7 +1780,7 @@
       <c r="B2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="47" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="20">
@@ -1593,24 +1804,24 @@
       <c r="J2" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="44"/>
-      <c r="L2" s="60" t="s">
+      <c r="K2" s="52"/>
+      <c r="L2" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="51"/>
-      <c r="N2" s="61" t="s">
+      <c r="M2" s="48"/>
+      <c r="N2" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="54" t="s">
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="51"/>
-      <c r="U2" s="54"/>
-      <c r="X2" s="54" t="s">
+      <c r="T2" s="48"/>
+      <c r="U2" s="51"/>
+      <c r="X2" s="51" t="s">
         <v>28</v>
       </c>
       <c r="Y2" s="43"/>
@@ -1622,10 +1833,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="60.75">
+    <row r="3" spans="1:28" ht="45.75">
       <c r="A3" s="20"/>
       <c r="B3" s="20"/>
-      <c r="C3" s="49"/>
+      <c r="C3" s="47"/>
       <c r="D3" s="20"/>
       <c r="E3" s="18" t="s">
         <v>32</v>
@@ -1645,22 +1856,22 @@
       <c r="J3" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="44"/>
-      <c r="L3" s="60" t="s">
+      <c r="K3" s="52"/>
+      <c r="L3" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="51"/>
-      <c r="N3" s="61" t="s">
+      <c r="M3" s="48"/>
+      <c r="N3" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="54"/>
-      <c r="X3" s="54"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="51"/>
+      <c r="X3" s="51"/>
       <c r="Y3" s="43"/>
       <c r="Z3" s="44"/>
       <c r="AA3" s="44" t="s">
@@ -1673,7 +1884,7 @@
     <row r="4" spans="1:28" ht="183">
       <c r="A4" s="20"/>
       <c r="B4" s="20"/>
-      <c r="C4" s="49"/>
+      <c r="C4" s="47"/>
       <c r="D4" s="20"/>
       <c r="E4" s="18" t="s">
         <v>36</v>
@@ -1681,10 +1892,10 @@
       <c r="F4" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="69">
+      <c r="G4" s="77">
         <v>137983</v>
       </c>
-      <c r="H4" s="69">
+      <c r="H4" s="77">
         <v>182000</v>
       </c>
       <c r="I4" s="17" t="s">
@@ -1693,23 +1904,23 @@
       <c r="J4" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="44"/>
-      <c r="L4" s="60" t="s">
+      <c r="K4" s="52"/>
+      <c r="L4" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="51"/>
-      <c r="N4" s="61" t="s">
+      <c r="M4" s="48"/>
+      <c r="N4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="54"/>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="45" t="s">
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="51"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="76" t="s">
         <v>39</v>
       </c>
       <c r="Z4" s="44"/>
@@ -1720,10 +1931,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="60.75">
+    <row r="5" spans="1:28" ht="45.75">
       <c r="A5" s="20"/>
       <c r="B5" s="20"/>
-      <c r="C5" s="49"/>
+      <c r="C5" s="47"/>
       <c r="D5" s="20"/>
       <c r="E5" s="18" t="s">
         <v>40</v>
@@ -1743,22 +1954,22 @@
       <c r="J5" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="44"/>
-      <c r="L5" s="60" t="s">
+      <c r="K5" s="52"/>
+      <c r="L5" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M5" s="51"/>
-      <c r="N5" s="61" t="s">
+      <c r="M5" s="48"/>
+      <c r="N5" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="51"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="51"/>
-      <c r="U5" s="54"/>
-      <c r="X5" s="54"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="51"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="51"/>
+      <c r="X5" s="51"/>
       <c r="Y5" s="43"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44" t="s">
@@ -1771,7 +1982,7 @@
     <row r="6" spans="1:28" ht="152.25">
       <c r="A6" s="20"/>
       <c r="B6" s="20"/>
-      <c r="C6" s="49"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="20"/>
       <c r="E6" s="18" t="s">
         <v>32</v>
@@ -1779,36 +1990,36 @@
       <c r="F6" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="69" t="s">
+      <c r="H6" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="77" t="s">
         <v>46</v>
       </c>
       <c r="J6" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="46"/>
-      <c r="L6" s="60" t="s">
+      <c r="K6" s="45"/>
+      <c r="L6" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="51"/>
-      <c r="N6" s="61" t="s">
+      <c r="M6" s="48"/>
+      <c r="N6" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="54"/>
-      <c r="X6" s="54"/>
-      <c r="Y6" s="47" t="s">
-        <v>39</v>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="51"/>
+      <c r="X6" s="51"/>
+      <c r="Y6" s="75" t="s">
+        <v>47</v>
       </c>
       <c r="Z6" s="44"/>
       <c r="AA6" s="44" t="s">
@@ -1821,47 +2032,47 @@
     <row r="7" spans="1:28" ht="213">
       <c r="A7" s="20"/>
       <c r="B7" s="20"/>
-      <c r="C7" s="49"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="20"/>
       <c r="E7" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="69">
+      <c r="G7" s="77">
         <v>4462</v>
       </c>
-      <c r="H7" s="69">
+      <c r="H7" s="77">
         <v>6195</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J7" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="46">
+      <c r="K7" s="45">
         <f>2460/6195</f>
         <v>0.39709443099273606</v>
       </c>
-      <c r="L7" s="60" t="s">
+      <c r="L7" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="51"/>
-      <c r="N7" s="61" t="s">
+      <c r="M7" s="48"/>
+      <c r="N7" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="54"/>
-      <c r="X7" s="54"/>
-      <c r="Y7" s="47" t="s">
-        <v>39</v>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="51"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="51"/>
+      <c r="X7" s="51"/>
+      <c r="Y7" s="74" t="s">
+        <v>50</v>
       </c>
       <c r="Z7" s="44"/>
       <c r="AA7" s="44" t="s">
@@ -1874,10 +2085,10 @@
     <row r="8" spans="1:28" ht="60.75">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
-      <c r="C8" s="49"/>
+      <c r="C8" s="47"/>
       <c r="D8" s="20"/>
       <c r="E8" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>33</v>
@@ -1886,31 +2097,33 @@
       <c r="H8" s="23">
         <v>60000</v>
       </c>
-      <c r="I8" s="48" t="s">
-        <v>50</v>
+      <c r="I8" s="46" t="s">
+        <v>52</v>
       </c>
       <c r="J8" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="44"/>
-      <c r="L8" s="60" t="s">
+      <c r="K8" s="52"/>
+      <c r="L8" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="51"/>
-      <c r="N8" s="61" t="s">
+      <c r="M8" s="48"/>
+      <c r="N8" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="54"/>
-      <c r="X8" s="54"/>
-      <c r="Y8" s="43"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="51"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="51"/>
+      <c r="X8" s="51"/>
+      <c r="Y8" s="65" t="s">
+        <v>53</v>
+      </c>
       <c r="Z8" s="44" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AA8" s="44" t="s">
         <v>31</v>
@@ -1919,16 +2132,16 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="60.75">
+    <row r="9" spans="1:28" ht="45.75">
       <c r="A9" s="20"/>
       <c r="B9" s="20"/>
-      <c r="C9" s="49"/>
+      <c r="C9" s="47"/>
       <c r="D9" s="20"/>
       <c r="E9" s="26" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G9" s="26">
         <v>0</v>
@@ -1936,29 +2149,31 @@
       <c r="H9" s="26">
         <v>713</v>
       </c>
-      <c r="I9" s="48" t="s">
-        <v>54</v>
+      <c r="I9" s="46" t="s">
+        <v>57</v>
       </c>
       <c r="J9" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K9" s="44"/>
-      <c r="L9" s="60" t="s">
+      <c r="K9" s="52"/>
+      <c r="L9" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M9" s="51"/>
-      <c r="N9" s="61" t="s">
+      <c r="M9" s="48"/>
+      <c r="N9" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="54"/>
-      <c r="X9" s="54"/>
-      <c r="Y9" s="43"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="51"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="65">
+        <v>713</v>
+      </c>
       <c r="Z9" s="44"/>
       <c r="AA9" s="44" t="s">
         <v>31</v>
@@ -1972,53 +2187,55 @@
         <v>135714</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>59</v>
       </c>
       <c r="D10" s="20">
         <v>2727783</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H10" s="23">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J10" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="44"/>
-      <c r="L10" s="60" t="s">
+      <c r="K10" s="52"/>
+      <c r="L10" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M10" s="51"/>
-      <c r="N10" s="61" t="s">
+      <c r="M10" s="48"/>
+      <c r="N10" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="51"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="54"/>
-      <c r="X10" s="55" t="s">
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="51"/>
+      <c r="X10" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="Y10" s="43"/>
+      <c r="Y10" s="65">
+        <v>250000</v>
+      </c>
       <c r="Z10" s="44" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AA10" s="44" t="s">
         <v>31</v>
@@ -2030,43 +2247,45 @@
     <row r="11" spans="1:28" ht="121.5">
       <c r="A11" s="20"/>
       <c r="B11" s="20"/>
-      <c r="C11" s="49"/>
+      <c r="C11" s="47"/>
       <c r="D11" s="20"/>
       <c r="E11" s="18" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K11" s="44"/>
-      <c r="L11" s="60" t="s">
+      <c r="K11" s="52"/>
+      <c r="L11" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M11" s="51"/>
-      <c r="N11" s="61" t="s">
+      <c r="M11" s="48"/>
+      <c r="N11" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="T11" s="51"/>
-      <c r="U11" s="54"/>
-      <c r="X11" s="55"/>
-      <c r="Y11" s="43"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" s="48"/>
+      <c r="U11" s="51"/>
+      <c r="X11" s="52"/>
+      <c r="Y11" s="65" t="s">
+        <v>67</v>
+      </c>
       <c r="Z11" s="44"/>
       <c r="AA11" s="44" t="s">
         <v>31</v>
@@ -2075,442 +2294,424 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="165">
+    <row r="12" spans="1:28" ht="138">
       <c r="A12" s="20"/>
       <c r="B12" s="20"/>
-      <c r="C12" s="49"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="20"/>
       <c r="E12" s="18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G12" s="26">
         <v>0</v>
       </c>
-      <c r="H12" s="69">
-        <v>0.3</v>
+      <c r="H12" s="77">
+        <v>0.2</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J12" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="44"/>
-      <c r="L12" s="60" t="s">
+      <c r="K12" s="52"/>
+      <c r="L12" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M12" s="51"/>
-      <c r="N12" s="61" t="s">
+      <c r="M12" s="48"/>
+      <c r="N12" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O12" s="51"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="T12" s="51"/>
-      <c r="U12" s="54"/>
-      <c r="X12" s="55"/>
-      <c r="Y12" s="40" t="s">
-        <v>67</v>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="T12" s="48"/>
+      <c r="U12" s="51"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="73" t="s">
+        <v>71</v>
       </c>
       <c r="Z12" s="44"/>
       <c r="AA12" s="44" t="s">
         <v>29</v>
       </c>
       <c r="AB12" s="44" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" ht="165">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="91.5">
       <c r="A13" s="20"/>
       <c r="B13" s="20"/>
-      <c r="C13" s="49"/>
+      <c r="C13" s="47"/>
       <c r="D13" s="20"/>
       <c r="E13" s="18" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G13" s="26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="18">
-        <v>0.2</v>
+        <v>500</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J13" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K13" s="44"/>
-      <c r="L13" s="60" t="s">
+      <c r="K13" s="52"/>
+      <c r="L13" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M13" s="51"/>
-      <c r="N13" s="61" t="s">
+      <c r="M13" s="48"/>
+      <c r="N13" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="51"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="T13" s="51"/>
-      <c r="U13" s="54"/>
-      <c r="X13" s="55"/>
-      <c r="Y13" s="40" t="s">
-        <v>67</v>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="51"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="51"/>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="43" t="s">
+        <v>76</v>
       </c>
       <c r="Z13" s="44"/>
-      <c r="AA13" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB13" s="44" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" ht="91.5">
+      <c r="AA13" s="44"/>
+      <c r="AB13" s="44"/>
+    </row>
+    <row r="14" spans="1:28" ht="121.5">
       <c r="A14" s="20"/>
       <c r="B14" s="20"/>
-      <c r="C14" s="49"/>
+      <c r="C14" s="47"/>
       <c r="D14" s="20"/>
       <c r="E14" s="18" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G14" s="26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="18">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J14" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="44"/>
-      <c r="L14" s="60" t="s">
+      <c r="K14" s="52"/>
+      <c r="L14" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M14" s="51"/>
-      <c r="N14" s="61" t="s">
+      <c r="M14" s="48"/>
+      <c r="N14" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="51"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="51"/>
-      <c r="U14" s="54"/>
-      <c r="X14" s="55"/>
-      <c r="Y14" s="43"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="51"/>
+      <c r="T14" s="48"/>
+      <c r="U14" s="51"/>
+      <c r="X14" s="52"/>
+      <c r="Y14" s="64" t="s">
+        <v>79</v>
+      </c>
       <c r="Z14" s="44"/>
-      <c r="AA14" s="44"/>
-      <c r="AB14" s="44"/>
-    </row>
-    <row r="15" spans="1:28" ht="104.1" customHeight="1">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="20"/>
+      <c r="AA14" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB14" s="44" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" ht="91.5">
+      <c r="A15" s="20">
+        <v>137393</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="20">
+        <v>463769</v>
+      </c>
       <c r="E15" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="26">
-        <v>1</v>
-      </c>
-      <c r="H15" s="18">
-        <v>6000</v>
+        <v>51</v>
+      </c>
+      <c r="F15" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="29">
+        <v>205000</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="44"/>
-      <c r="L15" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="K15" s="62">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L15" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M15" s="51"/>
-      <c r="N15" s="61" t="s">
+      <c r="M15" s="48"/>
+      <c r="N15" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="51"/>
-      <c r="S15" s="54"/>
-      <c r="T15" s="51"/>
-      <c r="U15" s="54"/>
-      <c r="X15" s="55"/>
-      <c r="Y15" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z15" s="44"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="T15" s="48"/>
+      <c r="U15" s="51"/>
+      <c r="X15" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y15" s="60">
+        <v>205000</v>
+      </c>
+      <c r="Z15" s="44" t="s">
+        <v>54</v>
+      </c>
       <c r="AA15" s="44" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AB15" s="44" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="91.5">
-      <c r="A16" s="20">
-        <v>137393</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="20">
-        <v>463769</v>
-      </c>
+      <c r="A16" s="66"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="66"/>
       <c r="E16" s="18" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G16" s="26">
-        <v>1</v>
+        <v>11200</v>
       </c>
       <c r="H16" s="26">
-        <v>80000</v>
-      </c>
-      <c r="I16" s="18"/>
+        <v>11200</v>
+      </c>
+      <c r="I16" s="26" t="s">
+        <v>88</v>
+      </c>
       <c r="J16" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="K16" s="44"/>
-      <c r="L16" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="K16" s="62">
+        <v>0.37</v>
+      </c>
+      <c r="L16" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M16" s="51"/>
-      <c r="N16" s="61" t="s">
+      <c r="M16" s="48"/>
+      <c r="N16" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O16" s="51"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="54"/>
-      <c r="T16" s="51"/>
-      <c r="U16" s="54"/>
-      <c r="X16" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y16" s="43"/>
-      <c r="Z16" s="44" t="s">
-        <v>51</v>
-      </c>
+      <c r="O16" s="48"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="48"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="T16" s="48"/>
+      <c r="U16" s="51"/>
+      <c r="X16" s="52"/>
+      <c r="Y16" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z16" s="44"/>
       <c r="AA16" s="44" t="s">
         <v>29</v>
       </c>
       <c r="AB16" s="44" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" ht="91.5">
+      <c r="A17" s="66"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="18" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="1:28" ht="60.75">
-      <c r="A17" s="62"/>
-      <c r="B17" s="62"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="18" t="s">
-        <v>23</v>
-      </c>
       <c r="F17" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26">
-        <v>11200</v>
-      </c>
-      <c r="I17" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="J17" s="20"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="26">
+        <v>4800</v>
+      </c>
+      <c r="H17" s="18">
+        <v>4800</v>
+      </c>
+      <c r="I17" s="18">
+        <v>4800</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="K17" s="62">
+        <v>0.32</v>
+      </c>
+      <c r="L17" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="51"/>
-      <c r="N17" s="61" t="s">
+      <c r="M17" s="48"/>
+      <c r="N17" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="51"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="51"/>
-      <c r="S17" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="T17" s="51"/>
-      <c r="U17" s="54"/>
-      <c r="X17" s="55"/>
-      <c r="Y17" s="43"/>
+      <c r="O17" s="48"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="T17" s="48"/>
+      <c r="U17" s="51"/>
+      <c r="X17" s="52"/>
+      <c r="Y17" s="43" t="s">
+        <v>91</v>
+      </c>
       <c r="Z17" s="44"/>
       <c r="AA17" s="44" t="s">
         <v>29</v>
       </c>
       <c r="AB17" s="44" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="91.5">
-      <c r="A18" s="62"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="62"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="20"/>
       <c r="E18" s="18" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="26"/>
-      <c r="H18" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" s="18"/>
+        <v>92</v>
+      </c>
+      <c r="G18" s="26">
+        <v>30</v>
+      </c>
+      <c r="H18" s="18">
+        <v>500</v>
+      </c>
+      <c r="I18" s="18">
+        <v>360</v>
+      </c>
       <c r="J18" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="K18" s="44"/>
-      <c r="L18" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="K18" s="62">
+        <v>0.37</v>
+      </c>
+      <c r="L18" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M18" s="51"/>
-      <c r="N18" s="61" t="s">
+      <c r="M18" s="48"/>
+      <c r="N18" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="51"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="54"/>
-      <c r="T18" s="51"/>
-      <c r="U18" s="54"/>
-      <c r="X18" s="55"/>
-      <c r="Y18" s="43"/>
+      <c r="O18" s="48"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="48"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="51"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="51"/>
+      <c r="X18" s="52"/>
+      <c r="Y18" s="43" t="s">
+        <v>93</v>
+      </c>
       <c r="Z18" s="44"/>
       <c r="AA18" s="44" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AB18" s="44" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" ht="91.5">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19" s="26">
-        <v>30</v>
-      </c>
-      <c r="H19" s="18">
-        <v>500</v>
-      </c>
-      <c r="I19" s="18"/>
-      <c r="J19" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="K19" s="44"/>
-      <c r="L19" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M19" s="51"/>
-      <c r="N19" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="O19" s="51"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="51"/>
-      <c r="S19" s="54"/>
-      <c r="T19" s="51"/>
-      <c r="U19" s="54"/>
-      <c r="X19" s="55"/>
-      <c r="Y19" s="43"/>
-      <c r="Z19" s="44"/>
-      <c r="AA19" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB19" s="44" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q19" xr:uid="{691AA1B1-7131-4DC9-B505-06DEB0F1B100}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q18" xr:uid="{691AA1B1-7131-4DC9-B505-06DEB0F1B100}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P19" xr:uid="{667CC0D2-5DB2-4955-9512-3F121442CF77}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P18" xr:uid="{667CC0D2-5DB2-4955-9512-3F121442CF77}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB19" xr:uid="{BA817B18-38C5-46B4-8B88-A9371871DCF9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB18" xr:uid="{BA817B18-38C5-46B4-8B88-A9371871DCF9}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA19 N2:N19" xr:uid="{2973EDA4-0FDC-41E2-8DCB-D39A6B55F5D9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N18 AA2:AA18" xr:uid="{2973EDA4-0FDC-41E2-8DCB-D39A6B55F5D9}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O19" xr:uid="{3E628846-858B-48A0-8F40-B26B197A9807}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O18" xr:uid="{3E628846-858B-48A0-8F40-B26B197A9807}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M19" xr:uid="{70AA7E24-B943-4553-B9F3-73CF8FB9D341}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M18" xr:uid="{70AA7E24-B943-4553-B9F3-73CF8FB9D341}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T19" xr:uid="{635AEBF2-B50B-4CF5-872B-F208FFDDE324}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T18" xr:uid="{635AEBF2-B50B-4CF5-872B-F208FFDDE324}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L19" xr:uid="{50CD920B-FA74-4A83-A4AF-A1AFAD0ED057}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L18" xr:uid="{50CD920B-FA74-4A83-A4AF-A1AFAD0ED057}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R19" xr:uid="{D1B9E9AD-4A8B-44C7-840E-0B5B5141FB0F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R18" xr:uid="{D1B9E9AD-4A8B-44C7-840E-0B5B5141FB0F}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S19" xr:uid="{3F85F021-B264-4738-9CF5-4F3636E48C65}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S18" xr:uid="{3F85F021-B264-4738-9CF5-4F3636E48C65}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{439D2B40-6D8F-4625-AA4B-B26EF78581BB}"/>
     <hyperlink ref="C10" r:id="rId2" xr:uid="{C35E0017-30AD-4965-AF4F-FF28C2DD5417}"/>
-    <hyperlink ref="C16" r:id="rId3" xr:uid="{EE575B42-21D8-495F-8205-68E2543171AE}"/>
+    <hyperlink ref="C15" r:id="rId3" xr:uid="{EE575B42-21D8-495F-8205-68E2543171AE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2520,13 +2721,13 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E20:E24</xm:sqref>
+          <xm:sqref>E19:E23</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C818BA62-241D-488A-A6F9-0D51B2584EFF}">
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E19</xm:sqref>
+          <xm:sqref>E2:E18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2585,10 +2786,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>13</v>
@@ -2607,16 +2808,16 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="60.75">
-      <c r="A2" s="67">
+      <c r="A2" s="71">
         <v>106770</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="67">
+      <c r="D2" s="71">
         <v>24261743</v>
       </c>
       <c r="E2" s="16" t="s">
@@ -2629,14 +2830,14 @@
         <v>26</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I2" s="19"/>
       <c r="J2" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K2" s="21"/>
-      <c r="L2" s="64" t="s">
+      <c r="L2" s="68" t="s">
         <v>28</v>
       </c>
       <c r="M2" s="14"/>
@@ -2648,12 +2849,12 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="30.75">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="67"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="16" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F3" s="18" t="s">
         <v>33</v>
@@ -2666,10 +2867,10 @@
       </c>
       <c r="I3" s="19"/>
       <c r="J3" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K3" s="21"/>
-      <c r="L3" s="65"/>
+      <c r="L3" s="69"/>
       <c r="M3" s="14"/>
       <c r="O3" t="s">
         <v>31</v>
@@ -2679,30 +2880,30 @@
       </c>
     </row>
     <row r="4" spans="1:19" ht="121.5">
-      <c r="A4" s="67"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="67"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="71"/>
       <c r="E4" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="69" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="69" t="s">
-        <v>92</v>
+      <c r="G4" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" s="77" t="s">
+        <v>100</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K4" s="21"/>
-      <c r="L4" s="65"/>
+      <c r="L4" s="69"/>
       <c r="M4" s="37" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="O4" t="s">
         <v>31</v>
@@ -2712,10 +2913,10 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="45.75">
-      <c r="A5" s="67"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="67"/>
+      <c r="A5" s="71"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="71"/>
       <c r="E5" s="16" t="s">
         <v>40</v>
       </c>
@@ -2730,10 +2931,10 @@
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K5" s="31"/>
-      <c r="L5" s="65"/>
+      <c r="L5" s="69"/>
       <c r="M5" s="34"/>
       <c r="O5" t="s">
         <v>31</v>
@@ -2743,30 +2944,30 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="106.5">
-      <c r="A6" s="67"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="67"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="71"/>
       <c r="E6" s="16" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="G6" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="69" t="s">
-        <v>95</v>
+        <v>102</v>
+      </c>
+      <c r="G6" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="77" t="s">
+        <v>104</v>
       </c>
       <c r="I6" s="19"/>
       <c r="J6" s="30" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="65"/>
+      <c r="L6" s="69"/>
       <c r="M6" s="38" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="O6" t="s">
         <v>31</v>
@@ -2776,32 +2977,32 @@
       </c>
     </row>
     <row r="7" spans="1:19" ht="121.5">
-      <c r="A7" s="67"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="67"/>
+      <c r="A7" s="71"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="71"/>
       <c r="E7" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="69" t="s">
-        <v>96</v>
-      </c>
-      <c r="H7" s="69" t="s">
+      <c r="G7" s="77" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="I7" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" s="30" t="s">
-        <v>27</v>
-      </c>
       <c r="K7" s="33"/>
-      <c r="L7" s="65"/>
+      <c r="L7" s="69"/>
       <c r="M7" s="38" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="O7" t="s">
         <v>31</v>
@@ -2811,30 +3012,30 @@
       </c>
     </row>
     <row r="8" spans="1:19" ht="30.75">
-      <c r="A8" s="67"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="67"/>
+      <c r="A8" s="71"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="71"/>
       <c r="E8" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>33</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H8" s="23">
         <v>60000</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K8" s="32"/>
-      <c r="L8" s="65"/>
+      <c r="L8" s="69"/>
       <c r="M8" s="35"/>
       <c r="O8" t="s">
         <v>31</v>
@@ -2844,15 +3045,15 @@
       </c>
     </row>
     <row r="9" spans="1:19" ht="45.75">
-      <c r="A9" s="67"/>
-      <c r="B9" s="67"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="67"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="71"/>
       <c r="E9" s="25" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G9" s="26">
         <v>0</v>
@@ -2861,13 +3062,13 @@
         <v>713</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K9" s="21"/>
-      <c r="L9" s="66"/>
+      <c r="L9" s="70"/>
       <c r="M9" s="14"/>
       <c r="O9" t="s">
         <v>31</v>
@@ -2881,34 +3082,34 @@
         <v>135714</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" s="27">
         <v>2727783</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H10" s="23">
         <v>100000</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K10" s="21"/>
-      <c r="L10" s="64" t="s">
+      <c r="L10" s="68" t="s">
         <v>28</v>
       </c>
       <c r="M10" s="14"/>
@@ -2928,20 +3129,20 @@
         <v>23</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K11" s="21"/>
-      <c r="L11" s="65"/>
+      <c r="L11" s="69"/>
       <c r="M11" s="14"/>
       <c r="O11" t="s">
         <v>31</v>
@@ -2956,31 +3157,31 @@
       <c r="C12" s="28"/>
       <c r="D12" s="27"/>
       <c r="E12" s="16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G12" s="26">
         <v>0</v>
       </c>
-      <c r="H12" s="69" t="s">
-        <v>101</v>
+      <c r="H12" s="77" t="s">
+        <v>111</v>
       </c>
       <c r="I12" s="18"/>
       <c r="J12" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K12" s="21"/>
-      <c r="L12" s="65"/>
+      <c r="L12" s="69"/>
       <c r="M12" s="40" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="O12" t="s">
         <v>29</v>
       </c>
       <c r="P12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="118.5" customHeight="1">
@@ -2989,31 +3190,31 @@
       <c r="C13" s="28"/>
       <c r="D13" s="27"/>
       <c r="E13" s="16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="G13" s="26">
         <v>2</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="I13" s="18"/>
       <c r="J13" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K13" s="21"/>
-      <c r="L13" s="65"/>
+      <c r="L13" s="69"/>
       <c r="M13" s="40" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="O13" t="s">
         <v>31</v>
       </c>
       <c r="P13" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="91.5">
@@ -3037,10 +3238,10 @@
         <v>75</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K14" s="21"/>
-      <c r="L14" s="65"/>
+      <c r="L14" s="69"/>
       <c r="M14" s="14"/>
     </row>
     <row r="15" spans="1:19" ht="104.1" customHeight="1">
@@ -3049,31 +3250,31 @@
       <c r="C15" s="28"/>
       <c r="D15" s="27"/>
       <c r="E15" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G15" s="26">
         <v>1</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I15" s="18"/>
       <c r="J15" s="20" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="K15" s="21"/>
-      <c r="L15" s="66"/>
+      <c r="L15" s="70"/>
       <c r="M15" s="39" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="O15" t="s">
         <v>31</v>
       </c>
       <c r="P15" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="91.5">
@@ -3081,32 +3282,32 @@
         <v>137393</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D16" s="27">
         <v>463769</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G16" s="26">
         <v>1</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="I16" s="18"/>
       <c r="J16" s="20" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K16" s="21"/>
-      <c r="L16" s="64" t="s">
+      <c r="L16" s="68" t="s">
         <v>28</v>
       </c>
       <c r="M16" s="14"/>
@@ -3114,67 +3315,67 @@
         <v>29</v>
       </c>
       <c r="P16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="67"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="67"/>
+      <c r="A17" s="71"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="71"/>
       <c r="E17" s="16" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="26">
         <v>11200</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="J17" s="20"/>
       <c r="K17" s="21"/>
-      <c r="L17" s="65"/>
+      <c r="L17" s="69"/>
       <c r="M17" s="14"/>
       <c r="O17" t="s">
         <v>29</v>
       </c>
       <c r="P17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="91.5">
+      <c r="A18" s="71"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="16" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="91.5">
-      <c r="A18" s="67"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="16" t="s">
-        <v>64</v>
-      </c>
       <c r="F18" s="18" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G18" s="26">
         <v>3</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="I18" s="18"/>
       <c r="J18" s="20" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K18" s="21"/>
-      <c r="L18" s="65"/>
+      <c r="L18" s="69"/>
       <c r="M18" s="14"/>
       <c r="O18" t="s">
         <v>29</v>
       </c>
       <c r="P18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="91.5">
@@ -3186,7 +3387,7 @@
         <v>73</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G19" s="26">
         <v>30</v>
@@ -3196,10 +3397,10 @@
       </c>
       <c r="I19" s="18"/>
       <c r="J19" s="20" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K19" s="21"/>
-      <c r="L19" s="66"/>
+      <c r="L19" s="70"/>
       <c r="M19" s="14"/>
       <c r="O19" t="s">
         <v>31</v>
@@ -3311,10 +3512,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="57.95">
@@ -3340,11 +3541,11 @@
         <v>26</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="57.95">
@@ -3353,20 +3554,20 @@
       <c r="C3" s="4"/>
       <c r="D3" s="3"/>
       <c r="E3" s="5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>35</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="57.95">
@@ -3381,14 +3582,14 @@
         <v>37</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="43.5">
@@ -3406,11 +3607,11 @@
         <v>42</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="72.599999999999994">
@@ -3419,20 +3620,20 @@
       <c r="C6" s="4"/>
       <c r="D6" s="3"/>
       <c r="E6" s="5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="87">
@@ -3441,22 +3642,22 @@
       <c r="C7" s="4"/>
       <c r="D7" s="3"/>
       <c r="E7" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="87">
@@ -3465,20 +3666,20 @@
       <c r="C8" s="4"/>
       <c r="D8" s="3"/>
       <c r="E8" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="72.599999999999994">
@@ -3487,20 +3688,20 @@
       <c r="C9" s="4"/>
       <c r="D9" s="3"/>
       <c r="E9" s="10" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G9" s="11">
         <v>0</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="101.45">
@@ -3508,31 +3709,31 @@
         <v>135714</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3">
         <v>2727783</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="101.45">
@@ -3544,17 +3745,17 @@
         <v>23</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="57.95">
@@ -3563,20 +3764,20 @@
       <c r="C12" s="4"/>
       <c r="D12" s="3"/>
       <c r="E12" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G12" s="11">
         <v>0</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="118.5" customHeight="1">
@@ -3585,20 +3786,20 @@
       <c r="C13" s="4"/>
       <c r="D13" s="3"/>
       <c r="E13" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="G13" s="11">
         <v>2</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="87">
@@ -3616,13 +3817,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>75</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="104.1" customHeight="1">
@@ -3631,20 +3832,20 @@
       <c r="C15" s="4"/>
       <c r="D15" s="3"/>
       <c r="E15" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G15" s="11">
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="9" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="87">
@@ -3652,29 +3853,29 @@
         <v>137393</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D16" s="3">
         <v>463769</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="G16" s="11">
         <v>1</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="87">
@@ -3683,20 +3884,20 @@
       <c r="C17" s="4"/>
       <c r="D17" s="3"/>
       <c r="E17" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="G17" s="11">
         <v>3</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="87">
@@ -3708,17 +3909,17 @@
         <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G18" s="11">
         <v>30</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -3753,179 +3954,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="49" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="53" t="s">
-        <v>125</v>
+      <c r="B2" s="50" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="53" t="s">
-        <v>126</v>
+      <c r="A3" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="70" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="53" t="s">
-        <v>128</v>
+      <c r="A4" s="78" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="70" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="53" t="s">
-        <v>130</v>
+      <c r="A5" s="78" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="53" t="s">
-        <v>131</v>
+      <c r="B6" s="50" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="53" t="s">
-        <v>132</v>
+      <c r="A7" s="78" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="53" t="s">
-        <v>133</v>
+      <c r="A8" s="78" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="53" t="s">
-        <v>134</v>
+      <c r="B9" s="50" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="70" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="71" t="s">
-        <v>136</v>
+      <c r="A10" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" s="79" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="70" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="71" t="s">
-        <v>138</v>
+      <c r="A11" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="79" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="70" t="s">
-        <v>139</v>
-      </c>
-      <c r="B12" s="53" t="s">
-        <v>140</v>
+      <c r="A12" s="78" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="70" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="71" t="s">
-        <v>141</v>
+      <c r="A13" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="79" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="70" t="s">
-        <v>142</v>
-      </c>
-      <c r="B14" s="71" t="s">
-        <v>143</v>
+      <c r="A14" s="78" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="79" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="70" t="s">
-        <v>144</v>
-      </c>
-      <c r="B15" s="71" t="s">
-        <v>145</v>
+      <c r="A15" s="78" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="79" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="71" t="s">
-        <v>146</v>
+      <c r="B16" s="79" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="70" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="53" t="s">
-        <v>147</v>
+      <c r="A17" s="78" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="70" t="s">
+      <c r="A18" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="71" t="s">
-        <v>148</v>
+      <c r="B18" s="79" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="70" t="s">
-        <v>149</v>
-      </c>
-      <c r="B19" s="71" t="s">
-        <v>150</v>
+      <c r="A19" s="78" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" s="79" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="70" t="s">
-        <v>151</v>
-      </c>
-      <c r="B20" s="71" t="s">
-        <v>152</v>
+      <c r="A20" s="78" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20" s="79" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="72" t="s">
-        <v>153</v>
+      <c r="B21" s="80" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="70" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" s="71" t="s">
-        <v>155</v>
+      <c r="A22" s="78" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22" s="79" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3934,17 +4135,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3969,6 +4161,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -4048,6 +4241,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -4191,6 +4389,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4240,11 +4447,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED76DDC8-0C2A-42A8-8991-BD9F8D7F2EB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8291C5C-93F9-4911-9A22-2BE485204320}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C583DE6-612A-4304-85D7-A23152D3FBED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED76DDC8-0C2A-42A8-8991-BD9F8D7F2EB1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Yemen - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Yemen - Energy Projects.xlsx
@@ -304,7 +304,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -523,9 +523,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -609,6 +606,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K10" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1455,9 +1472,8 @@
           <t>EU, SIDA</t>
         </is>
       </c>
-      <c r="O7" s="45">
-        <f>2460/6195</f>
-        <v/>
+      <c r="O7" s="45" t="n">
+        <v>0.3970944309927361</v>
       </c>
       <c r="P7" s="48" t="n"/>
       <c r="Q7" s="58" t="inlineStr">
@@ -1644,15 +1660,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K10" s="26" t="n">
+      <c r="K10" s="82" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="82" t="n"/>
-      <c r="M10" s="83" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M10" s="46" t="n"/>
       <c r="N10" s="20" t="n"/>
       <c r="O10" s="52" t="n"/>
       <c r="P10" s="48" t="n"/>
@@ -2138,10 +2150,10 @@
       </c>
     </row>
     <row r="17" ht="91.5" customHeight="1">
-      <c r="A17" s="32" t="n"/>
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
+      <c r="A17" s="66" t="n"/>
+      <c r="B17" s="66" t="n"/>
+      <c r="C17" s="67" t="n"/>
+      <c r="D17" s="66" t="n"/>
       <c r="E17" s="66" t="n"/>
       <c r="F17" s="66" t="n"/>
       <c r="G17" s="66" t="n"/>
@@ -2212,14 +2224,6 @@
       </c>
     </row>
     <row r="18" ht="91.5" customHeight="1">
-      <c r="A18" s="32" t="n"/>
-      <c r="B18" s="32" t="n"/>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="n"/>
-      <c r="G18" s="32" t="n"/>
-      <c r="H18" s="32" t="n"/>
       <c r="I18" s="18" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -2353,13 +2357,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B16:B17"/>
-  </mergeCells>
-  <dataValidations count="13">
+  <dataValidations count="11">
     <dataValidation sqref="Q2:Q18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -2393,17 +2391,12 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2581,10 +2574,10 @@
       </c>
     </row>
     <row r="3" ht="30.75" customHeight="1">
-      <c r="A3" s="84" t="n"/>
-      <c r="B3" s="84" t="n"/>
-      <c r="C3" s="84" t="n"/>
-      <c r="D3" s="84" t="n"/>
+      <c r="A3" s="83" t="n"/>
+      <c r="B3" s="83" t="n"/>
+      <c r="C3" s="83" t="n"/>
+      <c r="D3" s="83" t="n"/>
       <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Agricultural Services</t>
@@ -2613,7 +2606,7 @@
         </is>
       </c>
       <c r="K3" s="21" t="n"/>
-      <c r="L3" s="84" t="n"/>
+      <c r="L3" s="83" t="n"/>
       <c r="M3" s="14" t="n"/>
       <c r="O3" t="inlineStr">
         <is>
@@ -2627,10 +2620,10 @@
       </c>
     </row>
     <row r="4" ht="121.5" customHeight="1">
-      <c r="A4" s="84" t="n"/>
-      <c r="B4" s="84" t="n"/>
-      <c r="C4" s="84" t="n"/>
-      <c r="D4" s="84" t="n"/>
+      <c r="A4" s="83" t="n"/>
+      <c r="B4" s="83" t="n"/>
+      <c r="C4" s="83" t="n"/>
+      <c r="D4" s="83" t="n"/>
       <c r="E4" s="16" t="inlineStr">
         <is>
           <t>Education Services</t>
@@ -2660,7 +2653,7 @@
         </is>
       </c>
       <c r="K4" s="21" t="n"/>
-      <c r="L4" s="84" t="n"/>
+      <c r="L4" s="83" t="n"/>
       <c r="M4" s="37" t="inlineStr">
         <is>
           <t>to the CO: Please estimate number of beneficiaries.</t>
@@ -2678,10 +2671,10 @@
       </c>
     </row>
     <row r="5" ht="45.75" customHeight="1">
-      <c r="A5" s="84" t="n"/>
-      <c r="B5" s="84" t="n"/>
-      <c r="C5" s="84" t="n"/>
-      <c r="D5" s="84" t="n"/>
+      <c r="A5" s="83" t="n"/>
+      <c r="B5" s="83" t="n"/>
+      <c r="C5" s="83" t="n"/>
+      <c r="D5" s="83" t="n"/>
       <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
@@ -2707,7 +2700,7 @@
         </is>
       </c>
       <c r="K5" s="31" t="n"/>
-      <c r="L5" s="84" t="n"/>
+      <c r="L5" s="83" t="n"/>
       <c r="M5" s="34" t="n"/>
       <c r="O5" t="inlineStr">
         <is>
@@ -2721,10 +2714,10 @@
       </c>
     </row>
     <row r="6" ht="106.5" customHeight="1">
-      <c r="A6" s="84" t="n"/>
-      <c r="B6" s="84" t="n"/>
-      <c r="C6" s="84" t="n"/>
-      <c r="D6" s="84" t="n"/>
+      <c r="A6" s="83" t="n"/>
+      <c r="B6" s="83" t="n"/>
+      <c r="C6" s="83" t="n"/>
+      <c r="D6" s="83" t="n"/>
       <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Agricultural Services</t>
@@ -2754,7 +2747,7 @@
         </is>
       </c>
       <c r="K6" s="22" t="n"/>
-      <c r="L6" s="84" t="n"/>
+      <c r="L6" s="83" t="n"/>
       <c r="M6" s="38" t="inlineStr">
         <is>
           <t>to the CO: Please estimate number of beneficiaries.</t>
@@ -2772,10 +2765,10 @@
       </c>
     </row>
     <row r="7" ht="121.5" customHeight="1">
-      <c r="A7" s="84" t="n"/>
-      <c r="B7" s="84" t="n"/>
-      <c r="C7" s="84" t="n"/>
-      <c r="D7" s="84" t="n"/>
+      <c r="A7" s="83" t="n"/>
+      <c r="B7" s="83" t="n"/>
+      <c r="C7" s="83" t="n"/>
+      <c r="D7" s="83" t="n"/>
       <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Water Services</t>
@@ -2810,7 +2803,7 @@
         </is>
       </c>
       <c r="K7" s="33" t="n"/>
-      <c r="L7" s="84" t="n"/>
+      <c r="L7" s="83" t="n"/>
       <c r="M7" s="38" t="inlineStr">
         <is>
           <t>to the CO: Please estimate number of beneficiaries.</t>
@@ -2828,10 +2821,10 @@
       </c>
     </row>
     <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="84" t="n"/>
-      <c r="B8" s="84" t="n"/>
-      <c r="C8" s="84" t="n"/>
-      <c r="D8" s="84" t="n"/>
+      <c r="A8" s="83" t="n"/>
+      <c r="B8" s="83" t="n"/>
+      <c r="C8" s="83" t="n"/>
+      <c r="D8" s="83" t="n"/>
       <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Health Services</t>
@@ -2861,7 +2854,7 @@
         </is>
       </c>
       <c r="K8" s="32" t="n"/>
-      <c r="L8" s="84" t="n"/>
+      <c r="L8" s="83" t="n"/>
       <c r="M8" s="35" t="n"/>
       <c r="O8" t="inlineStr">
         <is>
@@ -3016,7 +3009,7 @@
         </is>
       </c>
       <c r="K11" s="21" t="n"/>
-      <c r="L11" s="84" t="n"/>
+      <c r="L11" s="83" t="n"/>
       <c r="M11" s="14" t="n"/>
       <c r="O11" t="inlineStr">
         <is>
@@ -3061,7 +3054,7 @@
         </is>
       </c>
       <c r="K12" s="21" t="n"/>
-      <c r="L12" s="84" t="n"/>
+      <c r="L12" s="83" t="n"/>
       <c r="M12" s="40" t="inlineStr">
         <is>
           <t>to the CO: Please estimate the number of MW (is this value per minigrid, or total?)
@@ -3112,7 +3105,7 @@
         </is>
       </c>
       <c r="K13" s="21" t="n"/>
-      <c r="L13" s="84" t="n"/>
+      <c r="L13" s="83" t="n"/>
       <c r="M13" s="40" t="inlineStr">
         <is>
           <t>to the CO: Please estimate the number of MW (is this value per minigrid, or total?)
@@ -3162,7 +3155,7 @@
         </is>
       </c>
       <c r="K14" s="21" t="n"/>
-      <c r="L14" s="84" t="n"/>
+      <c r="L14" s="83" t="n"/>
       <c r="M14" s="14" t="n"/>
     </row>
     <row r="15" ht="104.1" customHeight="1">
@@ -3301,7 +3294,7 @@
       </c>
       <c r="J17" s="20" t="n"/>
       <c r="K17" s="21" t="n"/>
-      <c r="L17" s="84" t="n"/>
+      <c r="L17" s="83" t="n"/>
       <c r="M17" s="14" t="n"/>
       <c r="O17" t="inlineStr">
         <is>
@@ -3346,7 +3339,7 @@
         </is>
       </c>
       <c r="K18" s="21" t="n"/>
-      <c r="L18" s="84" t="n"/>
+      <c r="L18" s="83" t="n"/>
       <c r="M18" s="14" t="n"/>
       <c r="O18" t="inlineStr">
         <is>
@@ -4143,288 +4136,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="85" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="85" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="86" t="inlineStr">
+      <c r="A2" s="85" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="86" t="inlineStr">
+      <c r="B2" s="85" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="86" t="inlineStr">
+      <c r="A3" s="85" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="86" t="inlineStr">
+      <c r="B3" s="85" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="86" t="inlineStr">
+      <c r="A4" s="85" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="86" t="inlineStr">
+      <c r="B4" s="85" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="85" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="85" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="86" t="inlineStr">
+      <c r="A6" s="85" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="86" t="inlineStr">
+      <c r="B6" s="85" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1">
-      <c r="A7" s="86" t="inlineStr">
+      <c r="A7" s="85" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="86" t="inlineStr">
+      <c r="B7" s="85" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="86" t="inlineStr">
+      <c r="A8" s="85" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="86" t="inlineStr">
+      <c r="B8" s="85" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1">
-      <c r="A9" s="86" t="inlineStr">
+      <c r="A9" s="85" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="86" t="inlineStr">
+      <c r="B9" s="85" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="86" t="inlineStr">
+      <c r="A10" s="85" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="86" t="inlineStr">
+      <c r="B10" s="85" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="86" t="inlineStr">
+      <c r="A11" s="85" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="86" t="inlineStr">
+      <c r="B11" s="85" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="86" t="inlineStr">
+      <c r="A12" s="85" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="86" t="inlineStr">
+      <c r="B12" s="85" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="86" t="inlineStr">
+      <c r="A13" s="85" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="86" t="inlineStr">
+      <c r="B13" s="85" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="86" t="inlineStr">
+      <c r="A14" s="85" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="86" t="inlineStr">
+      <c r="B14" s="85" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="86" t="inlineStr">
+      <c r="A15" s="85" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="86" t="inlineStr">
+      <c r="B15" s="85" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="86" t="inlineStr">
+      <c r="A16" s="85" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="86" t="inlineStr">
+      <c r="B16" s="85" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="86" t="inlineStr">
+      <c r="A17" s="85" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="86" t="inlineStr">
+      <c r="B17" s="85" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="86" t="inlineStr">
+      <c r="A18" s="85" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="86" t="inlineStr">
+      <c r="B18" s="85" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76.5" customHeight="1">
-      <c r="A19" s="86" t="inlineStr">
+      <c r="A19" s="85" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="86" t="inlineStr">
+      <c r="B19" s="85" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1">
-      <c r="A20" s="86" t="inlineStr">
+      <c r="A20" s="85" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="86" t="inlineStr">
+      <c r="B20" s="85" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45.75" customHeight="1">
-      <c r="A21" s="86" t="inlineStr">
+      <c r="A21" s="85" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="86" t="inlineStr">
+      <c r="B21" s="85" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="86" t="inlineStr">
+      <c r="A22" s="85" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="86" t="inlineStr">
+      <c r="B22" s="85" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="86" t="inlineStr">
+      <c r="A23" s="85" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="86" t="inlineStr">
+      <c r="B23" s="85" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="86" t="inlineStr">
+      <c r="A24" s="85" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="86" t="inlineStr">
+      <c r="B24" s="85" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
